--- a/leo-e1t4/Leo_My_Expressions.xlsx
+++ b/leo-e1t4/Leo_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4107,7 +4107,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -4117,15 +4117,19 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Expressions</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr"/>
+          <t>It's been one of those weeks where ~</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>~한 그런 한 주였어요</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -4135,15 +4139,19 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>20 Minutes</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr"/>
+          <t>Most of my time went into ~</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>시간 대부분이 ~에 들어갔어요</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -4153,19 +4161,19 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>at the beginning</t>
+          <t>I finally got around to ~</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>처음에는 At the beginning, it was really hard to stay consistent.</t>
+          <t>드디어 ~까지 손이 갔어요</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -4175,19 +4183,19 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>to be honest</t>
+          <t>The moment I got to ~, I ~</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>솔직히 말하면 To be honest, I wasn't sure I'd stick with it.</t>
+          <t>~에 도착하자마자 ~했어요</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -4197,19 +4205,19 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>kind of / sort of</t>
+          <t>What caught me off guard was ~</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>약간, 어느 정도 It's kind of overwhelming at first.</t>
+          <t>뜻밖이었던 건 ~였어요</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -4219,19 +4227,19 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>by the way</t>
+          <t>It was nothing like ~</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>그런데, 참고로 By the way, have you been to Okinawa before?</t>
+          <t>~랑은 전혀 달랐어요</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -4241,19 +4249,19 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>for a while</t>
+          <t>I ended up ~ing</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>한동안, 꽤 오랫동안 I've been working out for a while now.</t>
+          <t>결국 ~하게 됐어요</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -4263,19 +4271,19 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>at least</t>
+          <t>I've been meaning to ~</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>적어도 I try to work out at least three times a week.</t>
+          <t>전부터 ~하려던 참이에요</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -4285,19 +4293,19 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>I mean</t>
+          <t>~ is high on my list</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>내 말은, 그러니까 I mean, it's not easy, but it's worth it.</t>
+          <t>~는 내 목록에서 위쪽이에요</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -4307,19 +4315,19 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>so far</t>
+          <t>If I could get ~ off, I'd ~</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>지금까지는 So far, the trip has been amazing.</t>
+          <t>~를 쉴 수 있다면 ~할 거예요</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -4329,19 +4337,15 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>instead of ~</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>대신에 I had fish instead of meat for dinner.</t>
-        </is>
-      </c>
+          <t>I’ve been thinking all about~ (soccer shoes)</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -4351,19 +4355,15 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>end up</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>결국 ~ 하게 되다 We ended up staying at the hotel all day.</t>
-        </is>
-      </c>
+          <t>deposit</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -4373,19 +4373,15 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>turn out</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>결국 ~ 이 되다 It turned out to be a really good trip.</t>
-        </is>
-      </c>
+          <t>budget allocation, budget scheduling</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -4395,19 +4391,15 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>no wonder</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>어쩐지, ~ 할 만하다 No wonder everyone recommends this place.</t>
-        </is>
-      </c>
+          <t>I’ve not done it before</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -4417,19 +4409,15 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>as long as ~</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>하기만 하면 As long as I stay consistent, I'll see results.</t>
-        </is>
-      </c>
+          <t>it took longer than expected</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -4439,19 +4427,15 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>even though ~</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>임에도 불구하고 Even though it was raining, we went outside.</t>
-        </is>
-      </c>
+          <t>all over the place</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -4461,19 +4445,15 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>once in a while</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>가끔, 이따금 I treat myself to a big meal once in a while.</t>
-        </is>
-      </c>
+          <t>concern</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -4483,19 +4463,15 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>in the end</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>결국에는 In the end, I'm really glad I kept going.</t>
-        </is>
-      </c>
+          <t>try not to push</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -4505,19 +4481,15 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>the thing is</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>문제는, 사실은 The thing is, I didn't have much confidence at first.</t>
-        </is>
-      </c>
+          <t>overly excited</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -4527,19 +4499,15 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>out of nowhere</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>갑자기, 뜬금없이 Out of nowhere, a guy at the gym started talking to me.</t>
-        </is>
-      </c>
+          <t>strict</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -4549,7 +4517,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Situations</t>
+          <t>&lt;!-- Slide number: 5 --&gt; WRAP Before We Close One line we keep Pick one sentence from today's Caught Today boxes — the one you'd actually say on a trip. One question back to you Which trip felt easier to talk about — the one you took, or the one you haven't?</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr"/>
@@ -4557,7 +4525,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Class 20</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -4567,14 +4535,10 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Hotel Check-in &amp; Restaurant</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>호텔 헬스장 외국인과 대화</t>
-        </is>
-      </c>
+          <t>dive into the conversation instead of watching the toolbox</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -4589,14 +4553,10 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>I have a reservation under my name.</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>제 이름으로 예약했어요.</t>
-        </is>
-      </c>
+          <t>Expressions</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -4611,14 +4571,10 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Is it possible to get a room with a view?</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>뷰 있는 방으로 받을 수 있을까요?</t>
-        </is>
-      </c>
+          <t>20 Minutes</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -4633,12 +4589,12 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Is breakfast included?</t>
+          <t>at the beginning</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>아침 식사가 포함되어 있나요?</t>
+          <t>처음에는 At the beginning, it was really hard to stay consistent.</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4611,12 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>What do you recommend here?</t>
+          <t>to be honest</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>여기서 뭘 추천하세요?</t>
+          <t>솔직히 말하면 To be honest, I wasn't sure I'd stick with it.</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4633,12 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>I'll go with that.</t>
+          <t>kind of / sort of</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>그걸로 할게요.</t>
+          <t>약간, 어느 정도 It's kind of overwhelming at first.</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4655,12 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>How long have you been working out?</t>
+          <t>by the way</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>운동한 지 얼마나 됐어요?</t>
+          <t>그런데, 참고로 By the way, have you been to Okinawa before?</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4677,12 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>I've been into it for a while now.</t>
+          <t>for a while</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>꽤 오랫동안 빠져있었어요.</t>
+          <t>한동안, 꽤 오랫동안 I've been working out for a while now.</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4699,12 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>At the beginning, it was really hard.</t>
+          <t>at least</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>처음에는 정말 힘들었어요.</t>
+          <t>적어도 I try to work out at least three times a week.</t>
         </is>
       </c>
     </row>
@@ -4765,12 +4721,12 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>To be honest, I used to be really skinny.</t>
+          <t>I mean</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>솔직히, 예전엔 정말 말랐었어요.</t>
+          <t>내 말은, 그러니까 I mean, it's not easy, but it's worth it.</t>
         </is>
       </c>
     </row>
@@ -4787,12 +4743,12 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>As long as you stay consistent, you'll see results.</t>
+          <t>so far</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>꾸준히 하기만 하면 결과가 보여요.</t>
+          <t>지금까지는 So far, the trip has been amazing.</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4765,12 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>By the way, do you know any good spots around here?</t>
+          <t>instead of ~</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>이 근처에 좋은 곳 알아요?</t>
+          <t>대신에 I had fish instead of meat for dinner.</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4787,12 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>English Expression</t>
+          <t>end up</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>한국어 뜻</t>
+          <t>결국 ~ 하게 되다 We ended up staying at the hotel all day.</t>
         </is>
       </c>
     </row>
@@ -4853,10 +4809,14 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr"/>
+          <t>turn out</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>결국 ~ 이 되다 It turned out to be a really good trip.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -4871,10 +4831,14 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>even though</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr"/>
+          <t>no wonder</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>어쩐지, ~ 할 만하다 No wonder everyone recommends this place.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -4889,12 +4853,12 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Quiz</t>
+          <t>as long as ~</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>→ A. 최근에</t>
+          <t>하기만 하면 As long as I stay consistent, I'll see results.</t>
         </is>
       </c>
     </row>
@@ -4911,12 +4875,12 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Answers</t>
+          <t>even though ~</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>→ A. 최근에</t>
+          <t>임에도 불구하고 Even though it was raining, we went outside.</t>
         </is>
       </c>
     </row>
@@ -4933,12 +4897,12 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>I've been going to the gym a lot recently.</t>
+          <t>once in a while</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>솔직히 말하면</t>
+          <t>가끔, 이따금 I treat myself to a big meal once in a while.</t>
         </is>
       </c>
     </row>
@@ -4955,10 +4919,14 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>instead of</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr"/>
+          <t>in the end</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>결국에는 In the end, I'm really glad I kept going.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -4973,10 +4941,14 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>as long as</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr"/>
+          <t>the thing is</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>문제는, 사실은 The thing is, I didn't have much confidence at first.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -4991,19 +4963,19 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Match the Expression with the Korean Meaning</t>
+          <t>out of nowhere</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>한국어 뜻</t>
+          <t>갑자기, 뜬금없이 Out of nowhere, a guy at the gym started talking to me.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5013,19 +4985,15 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Free-Flow Speaking</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>지난주 표현 + 새로운 표현까지 모두 사용해서 자유롭게 대화해봐요!</t>
-        </is>
-      </c>
+          <t>Situations</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5035,19 +5003,19 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Exploring Okinawa</t>
+          <t>Hotel Check-in &amp; Restaurant</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>여행 중 새로 만난 사람과 저녁 식사</t>
+          <t>호텔 헬스장 외국인과 대화</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5057,19 +5025,19 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>What brings you to Okinawa?</t>
+          <t>I have a reservation under my name.</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>오키나와엔 무슨 일로 왔어요?</t>
+          <t>제 이름으로 예약했어요.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5079,19 +5047,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>I've been looking forward to this trip.</t>
+          <t>Is it possible to get a room with a view?</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>이 여행을 정말 기대하고 있었어요.</t>
+          <t>뷰 있는 방으로 받을 수 있을까요?</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5101,19 +5069,19 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Make the most of your time here!</t>
+          <t>Is breakfast included?</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>여기서의 시간을 최대한 즐겨요!</t>
+          <t>아침 식사가 포함되어 있나요?</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5123,19 +5091,19 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>I ended up staying longer than I planned.</t>
+          <t>What do you recommend here?</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>계획보다 더 오래 있게 됐어요.</t>
+          <t>여기서 뭘 추천하세요?</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5145,19 +5113,19 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>It turned out to be an amazing place.</t>
+          <t>I'll go with that.</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>정말 멋진 곳이더라고요.</t>
+          <t>그걸로 할게요.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5167,19 +5135,19 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>At some point, I want to come back.</t>
+          <t>How long have you been working out?</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>언젠가는 꼭 다시 오고 싶어요.</t>
+          <t>운동한 지 얼마나 됐어요?</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5189,19 +5157,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>No wonder everyone recommends this spot.</t>
+          <t>I've been into it for a while now.</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>어쩐지 다들 여기를 추천하더라고요.</t>
+          <t>꽤 오랫동안 빠져있었어요.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5211,19 +5179,19 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>We should catch up more over dinner.</t>
+          <t>At the beginning, it was really hard.</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>저녁 먹으면서 더 얘기해봐요.</t>
+          <t>처음에는 정말 힘들었어요.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5233,19 +5201,19 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>That makes sense — I totally get that.</t>
+          <t>To be honest, I used to be really skinny.</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>그렇군요, 완전히 이해돼요.</t>
+          <t>솔직히, 예전엔 정말 말랐었어요.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5255,19 +5223,19 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>The thing is, I used to be really shy.</t>
+          <t>As long as you stay consistent, you'll see results.</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>사실은, 예전엔 정말 수줍음이 많았어요.</t>
+          <t>꾸준히 하기만 하면 결과가 보여요.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5277,19 +5245,19 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>I'm still figuring out what I want to do.</t>
+          <t>By the way, do you know any good spots around here?</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>아직 뭘 하고 싶은지 알아가는 중이에요.</t>
+          <t>이 근처에 좋은 곳 알아요?</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5299,39 +5267,507 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>It's about time I tried something new.</t>
+          <t>English Expression</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>이제 새로운 걸 시도해볼 때가 됐어요.</t>
+          <t>한국어 뜻</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>used to</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>even though</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>→ A. 최근에</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>→ A. 최근에</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>I've been going to the gym a lot recently.</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>솔직히 말하면</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>instead of</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>as long as</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Match the Expression with the Korean Meaning</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>한국어 뜻</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>일상·사교</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Free-Flow Speaking</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>지난주 표현 + 새로운 표현까지 모두 사용해서 자유롭게 대화해봐요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Exploring Okinawa</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>여행 중 새로 만난 사람과 저녁 식사</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>What brings you to Okinawa?</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>오키나와엔 무슨 일로 왔어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>I've been looking forward to this trip.</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>이 여행을 정말 기대하고 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Make the most of your time here!</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>여기서의 시간을 최대한 즐겨요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>I ended up staying longer than I planned.</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>계획보다 더 오래 있게 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>It turned out to be an amazing place.</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>정말 멋진 곳이더라고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>At some point, I want to come back.</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>언젠가는 꼭 다시 오고 싶어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>No wonder everyone recommends this spot.</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>어쩐지 다들 여기를 추천하더라고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>We should catch up more over dinner.</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>저녁 먹으면서 더 얘기해봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>That makes sense — I totally get that.</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>그렇군요, 완전히 이해돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>The thing is, I used to be really shy.</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>사실은, 예전엔 정말 수줍음이 많았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>I'm still figuring out what I want to do.</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>아직 뭘 하고 싶은지 알아가는 중이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>It's about time I tried something new.</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>이제 새로운 걸 시도해볼 때가 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
         <is>
           <t>Even though it was hard, I kept going.</t>
         </is>
       </c>
-      <c r="D228" s="3" t="inlineStr">
+      <c r="D250" s="3" t="inlineStr">
         <is>
           <t>힘들었지만, 그래도 계속했어요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D228"/>
+  <autoFilter ref="A1:D250"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>